--- a/data-manipulation-scripts/sheets-cleanup/sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/MANGUEIRA FLEXIVEL FREIO 11_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>MANGUEIRA FREIO DIANTEIRO SMARTFOX FACTOR125 EC 2009 A 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -570,7 +573,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
